--- a/entregables/TCNB_series_calibracion_v2.xlsx
+++ b/entregables/TCNB_series_calibracion_v2.xlsx
@@ -495,7 +495,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A64"/>
+  <dimension ref="A1:A70"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -704,160 +704,156 @@
     <row r="33">
       <c r="A33" s="4" t="inlineStr">
         <is>
-          <t>LAS COLUMNAS "visible IBK"</t>
+          <t>LAS COLUMNAS "nodo observado"</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>Las tres fuentes del nodo -el 360, la cuenta sueldo y PLIN- son INTERNAS de</t>
+          <t>El nodo N1/N2/N3 sale de tres fuentes que son INTERNAS de Interbank: el 360, la</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>Interbank. A un cliente que IBK no ve, el nodo se lo arma desde la ausencia:</t>
+          <t>cuenta sueldo y PLIN. Eso parte a la poblacion en dos:</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="3" t="inlineStr">
-        <is>
-          <t>pasivo=0, cs=0, plin=0, que por el CASE cae en N3. Medido sobre la poblacion</t>
-        </is>
-      </c>
+      <c r="A36" s="3" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>de estas hojas, sin dato en NINGUNA de las tres fuentes:</t>
+          <t xml:space="preserve">  nodo OBSERVADO   IBK tiene datos de esa persona. Si sus banderas dan cero, es</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Interbank 9.7%   ·   BCP 62.2%   ·   Scotiabank 63.1%   ·   BBVA 61.2%</t>
+      <c r="A38" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                   un cero de verdad: no tiene cuenta sueldo, no usa PLIN. El</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Falabella 55.7%</t>
+      <c r="A39" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                   nodo mide comportamiento.</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>Por eso el nodo se va a N3 en 88-93% fuera de IBK contra 55% adentro. No es que</t>
+          <t xml:space="preserve">  nodo SUPUESTO    IBK no la ve. Las banderas dan cero por falta de informacion,</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>esos clientes sean peores: es que IBK no los ve.</t>
+          <t xml:space="preserve">                   no por comportamiento, y el CASE manda ese caso a N3 igual.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="3" t="inlineStr"/>
+      <c r="A42" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">                   El nodo mide cuanto la ve Interbank, no como se comporta.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
-      <c r="A43" s="3" t="inlineStr">
-        <is>
-          <t>Las columnas "visible IBK" repiten el calculo solo sobre los clientes con dato</t>
-        </is>
-      </c>
+      <c r="A43" s="3" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>en el 360, donde el nodo si dice algo. Ahi el nodo se parece al de IBK y el</t>
+          <t>Cuanto pesa el segundo caso, sin dato en NINGUNA de las tres fuentes:</t>
         </is>
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="3" t="inlineStr">
-        <is>
-          <t>desvio se corta casi a la mitad:</t>
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Interbank 9.7%   ·   BCP 62.2%   ·   Scotiabank 63.1%   ·   BBVA 61.2%</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t xml:space="preserve">   SSFF con BCP  EC +50.2% -&gt; +29.9%      SSFF sin BCP  +16.7% -&gt; +4.5%</t>
+          <t xml:space="preserve">   Falabella 55.7%</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   BBVA          EC +31.4% -&gt; +14.5%      BCP           +202.1% -&gt; +154.9%</t>
+      <c r="A47" s="3" t="inlineStr">
+        <is>
+          <t>Por eso el nodo se va a N3 en 88-93% fuera de IBK contra 55% adentro. No es que</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t xml:space="preserve">   Interbank     EC  -9.3% -&gt;  -8.6%   (casi no se mueve: ya es 90% visible)</t>
+      <c r="A48" s="3" t="inlineStr">
+        <is>
+          <t>esos clientes sean peores: es que IBK no los ve.</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>La mitad del desvio de SS.FF. no era riesgo, era ceguera. BCP sigue afuera de</t>
-        </is>
-      </c>
+      <c r="A49" s="3" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="3" t="inlineStr">
         <is>
-          <t>rango en las dos lecturas, asi que ahi si hay una diferencia real.</t>
+          <t>Las columnas "nodo observado" repiten todo el calculo solo sobre el primer</t>
         </is>
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="3" t="inlineStr"/>
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>grupo. Ahi el nodo se parece al de IBK y el desvio se corta casi a la mitad:</t>
+        </is>
+      </c>
     </row>
     <row r="52">
-      <c r="A52" s="4" t="inlineStr">
-        <is>
-          <t>PROYECCION DE LA MORA</t>
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   SSFF con BCP  EC +50.2% -&gt; +29.9%      SSFF sin BCP  +16.7% -&gt; +4.5%</t>
         </is>
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="3" t="inlineStr">
-        <is>
-          <t>Los meses sin mora 12m cerrada se proyectan por chain-ladder: se toma el ultimo</t>
+      <c r="A53" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   BBVA          EC +31.4% -&gt; +14.5%      BCP           +202.1% -&gt; +154.9%</t>
         </is>
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="3" t="inlineStr">
-        <is>
-          <t>horizonte con dato y se multiplica por el factor h-&gt;12 de la propia hoja.</t>
+      <c r="A54" s="5" t="inlineStr">
+        <is>
+          <t xml:space="preserve">   Interbank     EC  -9.3% -&gt;  -8.6%   (casi no se mueve: ya es 90% visible)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>V1, V2 y V3 son el P25, la mediana y el P75 de los factores historicos, y solo</t>
+          <t>La mitad del desvio de SS.FF. no era riesgo, era ceguera. BCP sigue afuera de</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>se calculan en las hojas de IBK.</t>
+          <t>rango en las dos lecturas, asi que ahi si hay una diferencia real.</t>
         </is>
       </c>
     </row>
@@ -867,35 +863,35 @@
     <row r="58">
       <c r="A58" s="4" t="inlineStr">
         <is>
-          <t>COLUMNAS CALCULADAS</t>
+          <t>PROYECCION DE LA MORA</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>EC vigente        PD cal vigente / mora 12m  - 1</t>
+          <t>Los meses sin mora 12m cerrada se proyectan por chain-ladder: se toma el ultimo</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>EC NUEVA          PD cal NUEVA   / mora 12m  - 1</t>
+          <t>horizonte con dato y se multiplica por el factor h-&gt;12 de la propia hoja.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>EC NUEVA vs proy  PD cal NUEVA   / proy      - 1   (para los meses sin mora cerrada)</t>
+          <t>V1, V2 y V3 son el P25, la mediana y el P75 de los factores historicos, y solo</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" s="3" t="inlineStr">
         <is>
-          <t>Son formulas vivas: si se edita una celda de entrada, el error se recalcula.</t>
+          <t>se calculan en las hojas de IBK.</t>
         </is>
       </c>
     </row>
@@ -903,7 +899,45 @@
       <c r="A63" s="3" t="inlineStr"/>
     </row>
     <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+      <c r="A64" s="4" t="inlineStr">
+        <is>
+          <t>COLUMNAS CALCULADAS</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>EC vigente        PD cal vigente / mora 12m  - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>EC NUEVA          PD cal NUEVA   / mora 12m  - 1</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>EC NUEVA vs proy  PD cal NUEVA   / proy      - 1   (para los meses sin mora cerrada)</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>Son formulas vivas: si se edita una celda de entrada, el error se recalcula.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>Generado por Programas/reportes/10_excel_series.py</t>
         </is>
@@ -967,6 +1001,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Las columnas "nodo observado" repiten el calculo solo sobre los clientes de los que Interbank tiene datos propios, unicos donde el nodo N1/N2/N3 se mide en vez de suponerse.</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -1075,17 +1116,17 @@
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>n visible IBK</t>
+          <t>n con nodo observado</t>
         </is>
       </c>
       <c r="W4" s="6" t="inlineStr">
         <is>
-          <t>PD cal NUEVA visible</t>
+          <t>PD cal NUEVA nodo observado</t>
         </is>
       </c>
       <c r="X4" s="6" t="inlineStr">
         <is>
-          <t>mora 12m visible</t>
+          <t>mora 12m nodo observado</t>
         </is>
       </c>
       <c r="Y4" s="6" t="inlineStr">
@@ -1105,7 +1146,7 @@
       </c>
       <c r="AB4" s="6" t="inlineStr">
         <is>
-          <t>EC NUEVA visible</t>
+          <t>EC NUEVA nodo observado</t>
         </is>
       </c>
     </row>
@@ -4587,6 +4628,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Las columnas "nodo observado" repiten el calculo solo sobre los clientes de los que Interbank tiene datos propios, unicos donde el nodo N1/N2/N3 se mide en vez de suponerse.</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -4695,17 +4743,17 @@
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>n visible IBK</t>
+          <t>n con nodo observado</t>
         </is>
       </c>
       <c r="W4" s="6" t="inlineStr">
         <is>
-          <t>PD cal NUEVA visible</t>
+          <t>PD cal NUEVA nodo observado</t>
         </is>
       </c>
       <c r="X4" s="6" t="inlineStr">
         <is>
-          <t>mora 12m visible</t>
+          <t>mora 12m nodo observado</t>
         </is>
       </c>
       <c r="Y4" s="6" t="inlineStr">
@@ -4725,7 +4773,7 @@
       </c>
       <c r="AB4" s="6" t="inlineStr">
         <is>
-          <t>EC NUEVA visible</t>
+          <t>EC NUEVA nodo observado</t>
         </is>
       </c>
     </row>
@@ -8207,6 +8255,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Las columnas "nodo observado" repiten el calculo solo sobre los clientes de los que Interbank tiene datos propios, unicos donde el nodo N1/N2/N3 se mide en vez de suponerse.</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -8315,17 +8370,17 @@
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>n visible IBK</t>
+          <t>n con nodo observado</t>
         </is>
       </c>
       <c r="W4" s="6" t="inlineStr">
         <is>
-          <t>PD cal NUEVA visible</t>
+          <t>PD cal NUEVA nodo observado</t>
         </is>
       </c>
       <c r="X4" s="6" t="inlineStr">
         <is>
-          <t>mora 12m visible</t>
+          <t>mora 12m nodo observado</t>
         </is>
       </c>
       <c r="Y4" s="6" t="inlineStr">
@@ -8345,7 +8400,7 @@
       </c>
       <c r="AB4" s="6" t="inlineStr">
         <is>
-          <t>EC NUEVA visible</t>
+          <t>EC NUEVA nodo observado</t>
         </is>
       </c>
     </row>
@@ -11827,6 +11882,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Las columnas "nodo observado" repiten el calculo solo sobre los clientes de los que Interbank tiene datos propios, unicos donde el nodo N1/N2/N3 se mide en vez de suponerse.</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -11935,17 +11997,17 @@
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>n visible IBK</t>
+          <t>n con nodo observado</t>
         </is>
       </c>
       <c r="W4" s="6" t="inlineStr">
         <is>
-          <t>PD cal NUEVA visible</t>
+          <t>PD cal NUEVA nodo observado</t>
         </is>
       </c>
       <c r="X4" s="6" t="inlineStr">
         <is>
-          <t>mora 12m visible</t>
+          <t>mora 12m nodo observado</t>
         </is>
       </c>
       <c r="Y4" s="6" t="inlineStr">
@@ -11965,7 +12027,7 @@
       </c>
       <c r="AB4" s="6" t="inlineStr">
         <is>
-          <t>EC NUEVA visible</t>
+          <t>EC NUEVA nodo observado</t>
         </is>
       </c>
     </row>
@@ -15447,6 +15509,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Las columnas "nodo observado" repiten el calculo solo sobre los clientes de los que Interbank tiene datos propios, unicos donde el nodo N1/N2/N3 se mide en vez de suponerse.</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -15555,17 +15624,17 @@
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>n visible IBK</t>
+          <t>n con nodo observado</t>
         </is>
       </c>
       <c r="W4" s="6" t="inlineStr">
         <is>
-          <t>PD cal NUEVA visible</t>
+          <t>PD cal NUEVA nodo observado</t>
         </is>
       </c>
       <c r="X4" s="6" t="inlineStr">
         <is>
-          <t>mora 12m visible</t>
+          <t>mora 12m nodo observado</t>
         </is>
       </c>
       <c r="Y4" s="6" t="inlineStr">
@@ -15585,7 +15654,7 @@
       </c>
       <c r="AB4" s="6" t="inlineStr">
         <is>
-          <t>EC NUEVA visible</t>
+          <t>EC NUEVA nodo observado</t>
         </is>
       </c>
     </row>
@@ -19102,32 +19171,32 @@
       </c>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>n visible IBK</t>
+          <t>n con nodo observado</t>
         </is>
       </c>
       <c r="K4" s="6" t="inlineStr">
         <is>
-          <t>% visible</t>
+          <t>% con nodo observado</t>
         </is>
       </c>
       <c r="L4" s="6" t="inlineStr">
         <is>
-          <t>PD NUEVA visible</t>
+          <t>PD cal NUEVA nodo observado</t>
         </is>
       </c>
       <c r="M4" s="6" t="inlineStr">
         <is>
-          <t>mora 12m visible</t>
+          <t>mora 12m nodo observado</t>
         </is>
       </c>
       <c r="N4" s="6" t="inlineStr">
         <is>
-          <t>EC NUEVA visible</t>
+          <t>EC NUEVA nodo observado</t>
         </is>
       </c>
       <c r="O4" s="6" t="inlineStr">
         <is>
-          <t>semaforo visible</t>
+          <t>semaforo nodo observado</t>
         </is>
       </c>
     </row>
@@ -20390,6 +20459,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Las columnas "nodo observado" repiten el calculo solo sobre los clientes de los que Interbank tiene datos propios, unicos donde el nodo N1/N2/N3 se mide en vez de suponerse.</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -20513,17 +20589,17 @@
       </c>
       <c r="Y4" s="6" t="inlineStr">
         <is>
-          <t>n visible IBK</t>
+          <t>n con nodo observado</t>
         </is>
       </c>
       <c r="Z4" s="6" t="inlineStr">
         <is>
-          <t>PD cal NUEVA visible</t>
+          <t>PD cal NUEVA nodo observado</t>
         </is>
       </c>
       <c r="AA4" s="6" t="inlineStr">
         <is>
-          <t>mora 12m visible</t>
+          <t>mora 12m nodo observado</t>
         </is>
       </c>
       <c r="AB4" s="6" t="inlineStr">
@@ -20543,7 +20619,7 @@
       </c>
       <c r="AE4" s="6" t="inlineStr">
         <is>
-          <t>EC NUEVA visible</t>
+          <t>EC NUEVA nodo observado</t>
         </is>
       </c>
     </row>
@@ -24199,6 +24275,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Las columnas "nodo observado" repiten el calculo solo sobre los clientes de los que Interbank tiene datos propios, unicos donde el nodo N1/N2/N3 se mide en vez de suponerse.</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -24322,17 +24405,17 @@
       </c>
       <c r="Y4" s="6" t="inlineStr">
         <is>
-          <t>n visible IBK</t>
+          <t>n con nodo observado</t>
         </is>
       </c>
       <c r="Z4" s="6" t="inlineStr">
         <is>
-          <t>PD cal NUEVA visible</t>
+          <t>PD cal NUEVA nodo observado</t>
         </is>
       </c>
       <c r="AA4" s="6" t="inlineStr">
         <is>
-          <t>mora 12m visible</t>
+          <t>mora 12m nodo observado</t>
         </is>
       </c>
       <c r="AB4" s="6" t="inlineStr">
@@ -24352,7 +24435,7 @@
       </c>
       <c r="AE4" s="6" t="inlineStr">
         <is>
-          <t>EC NUEVA visible</t>
+          <t>EC NUEVA nodo observado</t>
         </is>
       </c>
     </row>
@@ -28008,6 +28091,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Las columnas "nodo observado" repiten el calculo solo sobre los clientes de los que Interbank tiene datos propios, unicos donde el nodo N1/N2/N3 se mide en vez de suponerse.</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -28131,17 +28221,17 @@
       </c>
       <c r="Y4" s="6" t="inlineStr">
         <is>
-          <t>n visible IBK</t>
+          <t>n con nodo observado</t>
         </is>
       </c>
       <c r="Z4" s="6" t="inlineStr">
         <is>
-          <t>PD cal NUEVA visible</t>
+          <t>PD cal NUEVA nodo observado</t>
         </is>
       </c>
       <c r="AA4" s="6" t="inlineStr">
         <is>
-          <t>mora 12m visible</t>
+          <t>mora 12m nodo observado</t>
         </is>
       </c>
       <c r="AB4" s="6" t="inlineStr">
@@ -28161,7 +28251,7 @@
       </c>
       <c r="AE4" s="6" t="inlineStr">
         <is>
-          <t>EC NUEVA visible</t>
+          <t>EC NUEVA nodo observado</t>
         </is>
       </c>
     </row>
@@ -31817,6 +31907,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Las columnas "nodo observado" repiten el calculo solo sobre los clientes de los que Interbank tiene datos propios, unicos donde el nodo N1/N2/N3 se mide en vez de suponerse.</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -31940,17 +32037,17 @@
       </c>
       <c r="Y4" s="6" t="inlineStr">
         <is>
-          <t>n visible IBK</t>
+          <t>n con nodo observado</t>
         </is>
       </c>
       <c r="Z4" s="6" t="inlineStr">
         <is>
-          <t>PD cal NUEVA visible</t>
+          <t>PD cal NUEVA nodo observado</t>
         </is>
       </c>
       <c r="AA4" s="6" t="inlineStr">
         <is>
-          <t>mora 12m visible</t>
+          <t>mora 12m nodo observado</t>
         </is>
       </c>
       <c r="AB4" s="6" t="inlineStr">
@@ -31970,7 +32067,7 @@
       </c>
       <c r="AE4" s="6" t="inlineStr">
         <is>
-          <t>EC NUEVA visible</t>
+          <t>EC NUEVA nodo observado</t>
         </is>
       </c>
     </row>
@@ -35623,6 +35720,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Las columnas "nodo observado" repiten el calculo solo sobre los clientes de los que Interbank tiene datos propios, unicos donde el nodo N1/N2/N3 se mide en vez de suponerse.</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -35731,17 +35835,17 @@
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>n visible IBK</t>
+          <t>n con nodo observado</t>
         </is>
       </c>
       <c r="W4" s="6" t="inlineStr">
         <is>
-          <t>PD cal NUEVA visible</t>
+          <t>PD cal NUEVA nodo observado</t>
         </is>
       </c>
       <c r="X4" s="6" t="inlineStr">
         <is>
-          <t>mora 12m visible</t>
+          <t>mora 12m nodo observado</t>
         </is>
       </c>
       <c r="Y4" s="6" t="inlineStr">
@@ -35761,7 +35865,7 @@
       </c>
       <c r="AB4" s="6" t="inlineStr">
         <is>
-          <t>EC NUEVA visible</t>
+          <t>EC NUEVA nodo observado</t>
         </is>
       </c>
     </row>
@@ -39243,6 +39347,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Las columnas "nodo observado" repiten el calculo solo sobre los clientes de los que Interbank tiene datos propios, unicos donde el nodo N1/N2/N3 se mide en vez de suponerse.</t>
+        </is>
+      </c>
+    </row>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="6" t="inlineStr">
         <is>
@@ -39351,17 +39462,17 @@
       </c>
       <c r="V4" s="6" t="inlineStr">
         <is>
-          <t>n visible IBK</t>
+          <t>n con nodo observado</t>
         </is>
       </c>
       <c r="W4" s="6" t="inlineStr">
         <is>
-          <t>PD cal NUEVA visible</t>
+          <t>PD cal NUEVA nodo observado</t>
         </is>
       </c>
       <c r="X4" s="6" t="inlineStr">
         <is>
-          <t>mora 12m visible</t>
+          <t>mora 12m nodo observado</t>
         </is>
       </c>
       <c r="Y4" s="6" t="inlineStr">
@@ -39381,7 +39492,7 @@
       </c>
       <c r="AB4" s="6" t="inlineStr">
         <is>
-          <t>EC NUEVA visible</t>
+          <t>EC NUEVA nodo observado</t>
         </is>
       </c>
     </row>
